--- a/vendor_map_tsc.xlsx
+++ b/vendor_map_tsc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Dot Com Packing Slips\1-Orders Before Extraction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AEEFCB-752D-4341-A45E-E46C1BDA84BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D47C74-797F-4247-A8F6-2AAE04E810C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="57600" windowHeight="15555" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="95">
   <si>
     <t>SKU</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t>PW-4PK</t>
-  </si>
-  <si>
-    <t>123119 (32oz SD)</t>
   </si>
   <si>
     <t>Super Duper</t>
@@ -667,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -683,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
         <v>70</v>
@@ -700,7 +697,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -711,7 +708,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -722,7 +719,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -733,7 +730,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -744,7 +741,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -755,7 +752,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -766,7 +763,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -777,7 +774,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -788,7 +785,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>77</v>
@@ -799,7 +796,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>78</v>
@@ -810,7 +807,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>79</v>
@@ -821,7 +818,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -832,7 +829,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -843,7 +840,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -854,7 +851,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -865,7 +862,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
@@ -876,7 +873,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -887,7 +884,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -898,7 +895,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -909,7 +906,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>15</v>
@@ -920,7 +917,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -931,7 +928,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -942,7 +939,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
@@ -953,7 +950,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
@@ -964,7 +961,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -975,7 +972,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -986,7 +983,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>81</v>
@@ -997,7 +994,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>21</v>
@@ -1008,7 +1005,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>22</v>
@@ -1019,7 +1016,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>23</v>
@@ -1030,7 +1027,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
@@ -1041,7 +1038,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>25</v>
@@ -1052,7 +1049,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>26</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>82</v>
@@ -1074,7 +1071,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>83</v>
@@ -1085,7 +1082,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>84</v>
@@ -1096,7 +1093,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>27</v>
@@ -1107,7 +1104,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -1129,7 +1126,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>86</v>
@@ -1140,7 +1137,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>87</v>
@@ -1151,7 +1148,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>88</v>
@@ -1162,7 +1159,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>29</v>
@@ -1173,18 +1170,18 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>31</v>
@@ -1195,7 +1192,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -1206,7 +1203,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1">
         <v>4430</v>
@@ -1217,7 +1214,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B49" s="1">
         <v>4442</v>
@@ -1228,7 +1225,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>33</v>
@@ -1239,7 +1236,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -1250,7 +1247,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B52" s="1">
         <v>4642</v>
@@ -1261,7 +1258,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>35</v>
@@ -1272,7 +1269,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B54" s="1">
         <v>4660</v>
@@ -1283,7 +1280,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="1">
         <v>6642</v>
@@ -1294,7 +1291,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>36</v>
@@ -1305,7 +1302,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" s="1">
         <v>6660</v>
@@ -1316,7 +1313,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>37</v>
@@ -1327,7 +1324,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>89</v>
@@ -1338,7 +1335,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
         <v>38</v>
@@ -1349,7 +1346,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
         <v>39</v>
@@ -1360,7 +1357,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
         <v>40</v>
@@ -1371,7 +1368,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
         <v>41</v>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
         <v>42</v>
@@ -1393,142 +1390,142 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>93</v>
-      </c>
-      <c r="B65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="1">
+        <v>123118</v>
+      </c>
+      <c r="C65" t="s">
         <v>90</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" t="s">
-        <v>43</v>
+        <v>92</v>
+      </c>
+      <c r="B66" s="1">
+        <v>123119</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>93</v>
-      </c>
-      <c r="B67" t="s">
-        <v>44</v>
+        <v>92</v>
+      </c>
+      <c r="B67" s="1">
+        <v>123124</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>52</v>
+        <v>92</v>
+      </c>
+      <c r="B75" t="s">
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>93</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>53</v>
+        <v>92</v>
+      </c>
+      <c r="B76" t="s">
+        <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C77" t="s">
         <v>69</v>
@@ -1536,10 +1533,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C78" t="s">
         <v>69</v>
@@ -1547,10 +1544,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
@@ -1558,12 +1555,34 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C82" t="s">
         <v>69</v>
       </c>
     </row>

--- a/vendor_map_tsc.xlsx
+++ b/vendor_map_tsc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Dot Com Packing Slips\1-Orders Before Extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D47C74-797F-4247-A8F6-2AAE04E810C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AEEFCB-752D-4341-A45E-E46C1BDA84BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="57600" windowHeight="15555" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="96">
   <si>
     <t>SKU</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>PW-4PK</t>
+  </si>
+  <si>
+    <t>123119 (32oz SD)</t>
   </si>
   <si>
     <t>Super Duper</t>
@@ -664,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -680,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
         <v>70</v>
@@ -697,7 +700,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -708,7 +711,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -719,7 +722,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -730,7 +733,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -741,7 +744,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -752,7 +755,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -763,7 +766,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -774,7 +777,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -785,7 +788,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>77</v>
@@ -796,7 +799,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>78</v>
@@ -807,7 +810,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>79</v>
@@ -818,7 +821,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -829,7 +832,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
@@ -840,7 +843,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -851,7 +854,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -862,7 +865,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
@@ -873,7 +876,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -884,7 +887,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -895,7 +898,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -906,7 +909,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>15</v>
@@ -917,7 +920,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -928,7 +931,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -939,7 +942,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
@@ -950,7 +953,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
@@ -961,7 +964,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -972,7 +975,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -983,7 +986,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>81</v>
@@ -994,7 +997,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>21</v>
@@ -1005,7 +1008,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>22</v>
@@ -1016,7 +1019,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>23</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
@@ -1038,7 +1041,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>25</v>
@@ -1049,7 +1052,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>26</v>
@@ -1060,7 +1063,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>82</v>
@@ -1071,7 +1074,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>83</v>
@@ -1082,7 +1085,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>84</v>
@@ -1093,7 +1096,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>27</v>
@@ -1104,7 +1107,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -1115,7 +1118,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>28</v>
@@ -1126,7 +1129,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>86</v>
@@ -1137,7 +1140,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>87</v>
@@ -1148,7 +1151,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>88</v>
@@ -1159,7 +1162,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>29</v>
@@ -1170,18 +1173,18 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>31</v>
@@ -1192,7 +1195,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>32</v>
@@ -1203,7 +1206,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" s="1">
         <v>4430</v>
@@ -1214,7 +1217,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B49" s="1">
         <v>4442</v>
@@ -1225,7 +1228,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>33</v>
@@ -1236,7 +1239,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>34</v>
@@ -1247,7 +1250,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B52" s="1">
         <v>4642</v>
@@ -1258,7 +1261,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>35</v>
@@ -1269,7 +1272,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" s="1">
         <v>4660</v>
@@ -1280,7 +1283,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B55" s="1">
         <v>6642</v>
@@ -1291,7 +1294,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>36</v>
@@ -1302,7 +1305,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B57" s="1">
         <v>6660</v>
@@ -1313,7 +1316,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>37</v>
@@ -1324,7 +1327,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>89</v>
@@ -1335,7 +1338,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B60" t="s">
         <v>38</v>
@@ -1346,7 +1349,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
         <v>39</v>
@@ -1357,7 +1360,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B62" t="s">
         <v>40</v>
@@ -1368,7 +1371,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
         <v>41</v>
@@ -1379,7 +1382,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
         <v>42</v>
@@ -1390,142 +1393,142 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" s="1">
-        <v>123118</v>
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" t="s">
         <v>92</v>
-      </c>
-      <c r="B66" s="1">
-        <v>123119</v>
-      </c>
-      <c r="C66" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" t="s">
         <v>92</v>
-      </c>
-      <c r="B67" s="1">
-        <v>123124</v>
-      </c>
-      <c r="C67" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" t="s">
         <v>92</v>
-      </c>
-      <c r="B68" t="s">
-        <v>43</v>
-      </c>
-      <c r="C68" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" t="s">
         <v>92</v>
-      </c>
-      <c r="B69" t="s">
-        <v>44</v>
-      </c>
-      <c r="C69" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
         <v>92</v>
-      </c>
-      <c r="B70" t="s">
-        <v>45</v>
-      </c>
-      <c r="C70" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" t="s">
         <v>92</v>
-      </c>
-      <c r="B71" t="s">
-        <v>46</v>
-      </c>
-      <c r="C71" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" t="s">
         <v>92</v>
-      </c>
-      <c r="B72" t="s">
-        <v>47</v>
-      </c>
-      <c r="C72" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>93</v>
+      </c>
+      <c r="B73" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73" t="s">
         <v>92</v>
-      </c>
-      <c r="B73" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" t="s">
         <v>92</v>
-      </c>
-      <c r="B74" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>92</v>
-      </c>
-      <c r="B75" t="s">
-        <v>50</v>
+        <v>93</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" t="s">
-        <v>51</v>
+        <v>93</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C77" t="s">
         <v>69</v>
@@ -1533,10 +1536,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C78" t="s">
         <v>69</v>
@@ -1544,10 +1547,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
@@ -1555,34 +1558,12 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>92</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C81" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>92</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C82" t="s">
         <v>69</v>
       </c>
     </row>

--- a/vendor_map_tsc.xlsx
+++ b/vendor_map_tsc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Dot Com Packing Slips\1-Orders Before Extraction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\Order-Splitter-v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AEEFCB-752D-4341-A45E-E46C1BDA84BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA448A1-57DC-47CA-92AF-4C59C8978637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="57600" windowHeight="15555" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
   <si>
     <t>SKU</t>
   </si>
@@ -313,6 +313,12 @@
   </si>
   <si>
     <t>Vendor</t>
+  </si>
+  <si>
+    <t>RS10</t>
+  </si>
+  <si>
+    <t>RS25</t>
   </si>
 </sst>
 </file>
@@ -667,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -835,10 +841,10 @@
         <v>93</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -846,10 +852,10 @@
         <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -857,7 +863,7 @@
         <v>93</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -868,7 +874,7 @@
         <v>93</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
         <v>60</v>
@@ -879,7 +885,7 @@
         <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
@@ -890,7 +896,7 @@
         <v>93</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
         <v>60</v>
@@ -900,8 +906,8 @@
       <c r="A20" t="s">
         <v>93</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C20" t="s">
         <v>60</v>
@@ -912,7 +918,7 @@
         <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>60</v>
@@ -922,8 +928,8 @@
       <c r="A22" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
+      <c r="B22" t="s">
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>60</v>
@@ -933,8 +939,8 @@
       <c r="A23" t="s">
         <v>93</v>
       </c>
-      <c r="B23" t="s">
-        <v>17</v>
+      <c r="B23" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C23" t="s">
         <v>60</v>
@@ -944,8 +950,8 @@
       <c r="A24" t="s">
         <v>93</v>
       </c>
-      <c r="B24" t="s">
-        <v>18</v>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C24" t="s">
         <v>60</v>
@@ -956,7 +962,7 @@
         <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>60</v>
@@ -967,32 +973,32 @@
         <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
+      <c r="B27" t="s">
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>81</v>
+      <c r="B28" t="s">
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1000,10 +1006,10 @@
         <v>93</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1011,7 +1017,7 @@
         <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
         <v>62</v>
@@ -1022,7 +1028,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>62</v>
@@ -1033,7 +1039,7 @@
         <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
@@ -1044,7 +1050,7 @@
         <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>62</v>
@@ -1055,7 +1061,7 @@
         <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
@@ -1066,10 +1072,10 @@
         <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1077,10 +1083,10 @@
         <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1088,7 +1094,7 @@
         <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
         <v>63</v>
@@ -1099,7 +1105,7 @@
         <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
         <v>63</v>
@@ -1110,7 +1116,7 @@
         <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
         <v>63</v>
@@ -1121,7 +1127,7 @@
         <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
         <v>63</v>
@@ -1132,10 +1138,10 @@
         <v>93</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1143,10 +1149,10 @@
         <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1154,7 +1160,7 @@
         <v>93</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
         <v>64</v>
@@ -1165,10 +1171,10 @@
         <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1176,10 +1182,10 @@
         <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1187,10 +1193,10 @@
         <v>93</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1198,18 +1204,18 @@
         <v>93</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>93</v>
       </c>
-      <c r="B48" s="1">
-        <v>4430</v>
+      <c r="B48" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C48" t="s">
         <v>66</v>
@@ -1219,8 +1225,8 @@
       <c r="A49" t="s">
         <v>93</v>
       </c>
-      <c r="B49" s="1">
-        <v>4442</v>
+      <c r="B49" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C49" t="s">
         <v>66</v>
@@ -1230,8 +1236,8 @@
       <c r="A50" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>33</v>
+      <c r="B50" s="1">
+        <v>4430</v>
       </c>
       <c r="C50" t="s">
         <v>66</v>
@@ -1241,8 +1247,8 @@
       <c r="A51" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>34</v>
+      <c r="B51" s="1">
+        <v>4442</v>
       </c>
       <c r="C51" t="s">
         <v>66</v>
@@ -1252,8 +1258,8 @@
       <c r="A52" t="s">
         <v>93</v>
       </c>
-      <c r="B52" s="1">
-        <v>4642</v>
+      <c r="B52" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C52" t="s">
         <v>66</v>
@@ -1264,7 +1270,7 @@
         <v>93</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
         <v>66</v>
@@ -1275,7 +1281,7 @@
         <v>93</v>
       </c>
       <c r="B54" s="1">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C54" t="s">
         <v>66</v>
@@ -1285,8 +1291,8 @@
       <c r="A55" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="1">
-        <v>6642</v>
+      <c r="B55" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C55" t="s">
         <v>66</v>
@@ -1296,8 +1302,8 @@
       <c r="A56" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>36</v>
+      <c r="B56" s="1">
+        <v>4660</v>
       </c>
       <c r="C56" t="s">
         <v>66</v>
@@ -1308,7 +1314,7 @@
         <v>93</v>
       </c>
       <c r="B57" s="1">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C57" t="s">
         <v>66</v>
@@ -1319,7 +1325,7 @@
         <v>93</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
@@ -1329,33 +1335,33 @@
       <c r="A59" t="s">
         <v>93</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>89</v>
+      <c r="B59" s="1">
+        <v>6660</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>93</v>
       </c>
-      <c r="B60" t="s">
-        <v>38</v>
+      <c r="B60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
-      <c r="B61" t="s">
-        <v>39</v>
+      <c r="B61" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1363,7 +1369,7 @@
         <v>93</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C62" t="s">
         <v>68</v>
@@ -1374,7 +1380,7 @@
         <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
         <v>68</v>
@@ -1385,7 +1391,7 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s">
         <v>68</v>
@@ -1396,10 +1402,10 @@
         <v>93</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1407,10 +1413,10 @@
         <v>93</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1418,10 +1424,10 @@
         <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1429,7 +1435,7 @@
         <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
         <v>92</v>
@@ -1440,7 +1446,7 @@
         <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
         <v>92</v>
@@ -1451,7 +1457,7 @@
         <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
         <v>92</v>
@@ -1462,7 +1468,7 @@
         <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C71" t="s">
         <v>92</v>
@@ -1473,7 +1479,7 @@
         <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
         <v>92</v>
@@ -1484,7 +1490,7 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
         <v>92</v>
@@ -1495,7 +1501,7 @@
         <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C74" t="s">
         <v>92</v>
@@ -1505,22 +1511,22 @@
       <c r="A75" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>52</v>
+      <c r="B75" t="s">
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>93</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>53</v>
+      <c r="B76" t="s">
+        <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1528,7 +1534,7 @@
         <v>93</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C77" t="s">
         <v>69</v>
@@ -1539,7 +1545,7 @@
         <v>93</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C78" t="s">
         <v>69</v>
@@ -1550,7 +1556,7 @@
         <v>93</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
@@ -1561,9 +1567,31 @@
         <v>93</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C82" t="s">
         <v>69</v>
       </c>
     </row>

--- a/vendor_map_tsc.xlsx
+++ b/vendor_map_tsc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OrderSplitter\Order-Splitter-v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA448A1-57DC-47CA-92AF-4C59C8978637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254357CA-088B-4335-871E-C37259C41B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
@@ -270,9 +270,6 @@
     <t>BGXF50</t>
   </si>
   <si>
-    <t>MMR32oz</t>
-  </si>
-  <si>
     <t>PenaShield SC</t>
   </si>
   <si>
@@ -319,6 +316,9 @@
   </si>
   <si>
     <t>RS25</t>
+  </si>
+  <si>
+    <t>MMR32</t>
   </si>
 </sst>
 </file>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
         <v>70</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>77</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>78</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>79</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>80</v>
@@ -838,10 +838,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -849,10 +849,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -860,7 +860,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -871,7 +871,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>10</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
@@ -904,7 +904,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -915,7 +915,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>13</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>15</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>20</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
         <v>62</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>21</v>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>22</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>23</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>24</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>25</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>26</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
         <v>63</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
         <v>63</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
         <v>63</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>27</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
         <v>63</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>28</v>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
         <v>64</v>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
         <v>64</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>64</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>29</v>
@@ -1201,18 +1201,18 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>31</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>32</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B50" s="1">
         <v>4430</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B51" s="1">
         <v>4442</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>33</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B54" s="1">
         <v>4642</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>35</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B56" s="1">
         <v>4660</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" s="1">
         <v>6642</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>36</v>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B59" s="1">
         <v>6660</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>37</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C61" t="s">
         <v>67</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
         <v>38</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
         <v>39</v>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
         <v>40</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
         <v>41</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
         <v>42</v>
@@ -1421,117 +1421,117 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" t="s">
         <v>90</v>
-      </c>
-      <c r="C67" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" t="s">
         <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B69" t="s">
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
         <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
         <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
         <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
         <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B76" t="s">
         <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>52</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>53</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>54</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>55</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>56</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>57</v>
